--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/NEW_JERSEY_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/NEW_JERSEY_2019.xlsx
@@ -11058,7 +11058,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C595">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C653">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C654">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C660">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C756">
